--- a/Result/profitability/3226.xlsx
+++ b/Result/profitability/3226.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.29</v>
       </c>
       <c r="M2" t="n">
-        <v>0.23375</v>
+        <v>0.10625</v>
       </c>
       <c r="N2" t="n">
-        <v>15.5375</v>
+        <v>12.95375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02374999999999999</v>
+        <v>-0.18</v>
       </c>
       <c r="N3" t="n">
-        <v>14.60375</v>
+        <v>12.265</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.145</v>
+        <v>-0.3425000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>14.28375</v>
+        <v>11.7725</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.13</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.43625</v>
+        <v>-0.29625</v>
       </c>
       <c r="N5" t="n">
-        <v>11.94625</v>
+        <v>10.64375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.61</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.325</v>
+        <v>-0.3675</v>
       </c>
       <c r="N6" t="n">
-        <v>13.125</v>
+        <v>13.76</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>-0.48</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.38</v>
+        <v>-0.50125</v>
       </c>
       <c r="N7" t="n">
-        <v>14.9025</v>
+        <v>13.3325</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-1.48</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6387499999999999</v>
+        <v>-0.6887500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>11.0825</v>
+        <v>10.595</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,10 +1645,10 @@
         <v>-0.99</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.90625</v>
+        <v>-0.9062500000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>7.181249999999999</v>
+        <v>7.18125</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,10 +1772,10 @@
         <v>-0.55</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.845</v>
+        <v>-0.8450000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>7.348749999999999</v>
+        <v>7.34875</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>-0.41</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8837499999999999</v>
+        <v>-0.88375</v>
       </c>
       <c r="N12" t="n">
         <v>7.34375</v>
@@ -2026,7 +2026,7 @@
         <v>-0.91</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.85625</v>
+        <v>-0.8562500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>8.02</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3226</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>295</v>
+      </c>
+      <c r="D75" t="n">
+        <v>285</v>
+      </c>
+      <c r="E75" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-8.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-25</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2224999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.49875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.5386740331491713</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7466666666666666</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-10.42</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.7572674418604651</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
